--- a/design/新世界观.xlsx
+++ b/design/新世界观.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\牛牛农场\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C4DF773-A548-4CD9-95CA-878015C2377D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E4A10E2-B12A-41D0-9EFD-D893ADDAB19B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="卡包" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,10 @@
     <sheet name="属性点" sheetId="5" r:id="rId5"/>
     <sheet name="任务" sheetId="7" r:id="rId6"/>
     <sheet name="新手引导" sheetId="8" r:id="rId7"/>
-    <sheet name="旅行护照" sheetId="6" r:id="rId8"/>
+    <sheet name="小偷" sheetId="9" r:id="rId8"/>
+    <sheet name="修改意见" sheetId="10" r:id="rId9"/>
+    <sheet name="旅行护照" sheetId="6" r:id="rId10"/>
+    <sheet name="成就" sheetId="11" r:id="rId11"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -35,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="296">
   <si>
     <t>人物卡</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -801,22 +804,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>攻击4，血量6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击6，血量4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击8，血量2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击2，血量8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>边牧+边牧+房屋</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -994,6 +981,241 @@
   </si>
   <si>
     <t>成功驱逐一个小偷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不来</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第1晚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小偷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>属性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大盗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>资本家</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>间谍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击1血量3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>价值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击2血量6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击3血量12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击4血量20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第2-5晚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小偷1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第6-10晚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小偷2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第11-15晚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小偷3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第16-20晚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大盗1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第21-25晚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大盗2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大盗3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第31-35晚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第26-30晚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>资本家1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第36-40晚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第41-45晚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第45-50晚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>资本家2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>资本家3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>间谍1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第51-55晚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第56-60晚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第61-65晚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第66-70晚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第71-75晚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第76-80晚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>间谍2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>间谍3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第80+晚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小偷刷新后，牧羊犬会自动去寻找小偷并攻击，击杀后获得相应金币奖励</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、新手引导挡住了卡牌，新手引导需要游戏开始直接引导</t>
+  </si>
+  <si>
+    <t>2、游戏最上面一行的内容需要做个悬停介绍</t>
+  </si>
+  <si>
+    <t>3、在图鉴内增加物品卖出价格表</t>
+  </si>
+  <si>
+    <t>4、按照表格的修改</t>
+  </si>
+  <si>
+    <t>5、换回原来的一个主游戏界面的玩法，不拆分关卡</t>
+  </si>
+  <si>
+    <t>点击开始游戏后，引导玩家打开新手礼包，牧民叠加树木，牧民叠加蓝莓丛，牧民叠加两个木头制作出木剑，牧羊犬叠加木剑增加属性，点击卡包购买一个动物店卡包，留下一句开始经营牧场吧，结束。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新手引导</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>游戏首页参考</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>游戏适配</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>改成横屏</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>先做个入口，内容下次加</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>先在开始游戏旁边做个入口，内容下次加</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>牧民+厨房+蓝莓1+面粉1+生肉1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>凯撒沙拉1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>牧民+凯撒沙拉1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>饱食+5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>牧羊犬+凯撒沙拉1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1095,7 +1317,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1160,6 +1382,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1175,6 +1406,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>234950</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>25070</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>3674864</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>2502</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="图片 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD671612-0D20-4853-B7A0-BDEA3357407F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1174750" y="2514270"/>
+          <a:ext cx="3439914" cy="1933232"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1486,7 +1766,7 @@
         <v>22</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="F3" s="18">
         <v>0.2</v>
@@ -1500,7 +1780,7 @@
         <v>23</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="F4" s="18">
         <v>0.2</v>
@@ -1514,7 +1794,7 @@
         <v>24</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F5" s="18">
         <v>0.2</v>
@@ -1528,7 +1808,7 @@
         <v>25</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="F6" s="18">
         <v>0.2</v>
@@ -1542,7 +1822,7 @@
         <v>54</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="F7" s="18">
         <v>0.2</v>
@@ -1787,9 +2067,41 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45E8EA59-5493-4893-9D74-B4AD4C40A092}">
+  <dimension ref="A2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98048FB5-612C-4B14-B0D9-46071F1DCBBE}">
+  <dimension ref="A2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>290</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C11E52B-E87E-463A-BA06-AF84768AE451}">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.6640625" style="2"/>
@@ -1799,15 +2111,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B1" s="21" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -1887,6 +2199,70 @@
         <v>65</v>
       </c>
       <c r="B12" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B19" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="1">
         <v>2</v>
       </c>
     </row>
@@ -2140,7 +2516,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51A00AD4-C122-43D6-8223-BD647DC0E625}">
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="43.5" style="2" bestFit="1" customWidth="1"/>
@@ -2552,6 +2928,15 @@
       </c>
       <c r="C41" s="15"/>
     </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="14" t="s">
+        <v>291</v>
+      </c>
+      <c r="B42" s="15" t="s">
+        <v>292</v>
+      </c>
+      <c r="C42" s="15"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2561,7 +2946,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D98782A8-ED8F-4BF9-9403-E57E1CFD33A1}">
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" style="2" bestFit="1" customWidth="1"/>
@@ -2579,7 +2964,7 @@
     </row>
     <row r="3" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="4" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2587,7 +2972,7 @@
         <v>82</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="5" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2595,7 +2980,7 @@
         <v>22</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="6" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2603,7 +2988,7 @@
         <v>23</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="7" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2611,7 +2996,7 @@
         <v>24</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2619,7 +3004,7 @@
         <v>25</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="9" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2627,7 +3012,7 @@
         <v>54</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="10" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2674,16 +3059,16 @@
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="B16" s="20" t="s">
-        <v>116</v>
+      <c r="A16" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B17" s="20" t="s">
         <v>116</v>
@@ -2691,15 +3076,15 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>182</v>
+        <v>116</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="B19" s="20" t="s">
         <v>182</v>
@@ -2707,82 +3092,98 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
-        <v>183</v>
+        <v>219</v>
       </c>
       <c r="B20" s="20" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
-        <v>185</v>
+        <v>295</v>
       </c>
       <c r="B21" s="20" t="s">
-        <v>186</v>
+        <v>294</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B22" s="20" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B23" s="20" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="B24" s="20" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="B25" s="20" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="B24" s="20" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="14" t="s">
-        <v>195</v>
-      </c>
-      <c r="B25" s="15" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="B26" s="15" t="s">
-        <v>203</v>
+      <c r="B26" s="20" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="14" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="14" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="14" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>207</v>
+        <v>201</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="B31" s="15" t="s">
+        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -2804,95 +3205,95 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
   </sheetData>
@@ -2903,25 +3304,268 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BABAB38C-20F4-43DE-B97E-DC12E08E513C}">
-  <dimension ref="A2:B3"/>
+  <dimension ref="A2:B13"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.4140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.33203125" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="71.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>224</v>
+        <v>215</v>
+      </c>
+      <c r="B3" s="24" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="42" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B7" s="24" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA4EA6F2-A72A-4C52-8A39-6EF124A0289C}">
+  <dimension ref="A2:C27"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.4140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.6640625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="23" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C5" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C6" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="C7" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C8" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>276</v>
       </c>
     </row>
   </sheetData>
@@ -2930,11 +3574,40 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45E8EA59-5493-4893-9D74-B4AD4C40A092}">
-  <dimension ref="A1"/>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BABE5CA-9387-4718-B16B-D6A5786F029B}">
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="50.75" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>283</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
